--- a/extraction/planilhas/despesa_operacional.xlsx
+++ b/extraction/planilhas/despesa_operacional.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -533,7 +533,6 @@
       <c r="E5" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -557,7 +556,6 @@
       <c r="E6" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -581,7 +579,6 @@
       <c r="E7" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -605,7 +602,6 @@
       <c r="E8" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -629,7 +625,6 @@
       <c r="E9" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -653,7 +648,6 @@
       <c r="E10" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -677,7 +671,6 @@
       <c r="E11" s="5" t="n">
         <v>997</v>
       </c>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -701,7 +694,6 @@
       <c r="E12" s="5" t="n">
         <v>204.87</v>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -725,7 +717,6 @@
       <c r="E13" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -749,7 +740,6 @@
       <c r="E14" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -773,7 +763,6 @@
       <c r="E15" s="5" t="n">
         <v>997</v>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -825,7 +814,6 @@
       <c r="E17" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -849,7 +837,6 @@
       <c r="E18" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -873,7 +860,6 @@
       <c r="E19" s="5" t="n">
         <v>997</v>
       </c>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -925,7 +911,6 @@
       <c r="E21" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -949,7 +934,6 @@
       <c r="E22" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -973,7 +957,6 @@
       <c r="E23" s="5" t="n">
         <v>997</v>
       </c>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -997,7 +980,6 @@
       <c r="E24" s="5" t="n">
         <v>271.2</v>
       </c>
-      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1021,7 +1003,6 @@
       <c r="E25" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -1045,7 +1026,6 @@
       <c r="E26" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -1069,7 +1049,6 @@
       <c r="E27" s="5" t="n">
         <v>997</v>
       </c>
-      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -1093,7 +1072,6 @@
       <c r="E28" s="5" t="n">
         <v>839.1799999999999</v>
       </c>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -1117,7 +1095,6 @@
       <c r="E29" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -1141,7 +1118,6 @@
       <c r="E30" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -1177,55 +1153,59 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>comum</t>
+          <t>shopee</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>pro_labore</t>
+          <t>midia_manual</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Pro labore</t>
+          <t>Shopee Ads</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
+        <v>88.91</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>parcial: 01 a 04/08, midia pausada desde entao</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>shopee</t>
+          <t>comum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>midia_manual</t>
+          <t>consultoria</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Shopee Ads</t>
+          <t>Consultoria</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>88.91</v>
+        <v>1114.53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>parcial: 01 a 04/08, midia pausada desde entao</t>
+          <t>rateio de contrato de 12 meses, total 13374.38</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>46266</v>
+        <v>46296</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1253,7 +1233,7 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>46296</v>
+        <v>46327</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1281,7 +1261,7 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>46327</v>
+        <v>46357</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1309,7 +1289,7 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
-        <v>46357</v>
+        <v>46388</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1337,7 +1317,7 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>46388</v>
+        <v>46419</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1365,7 +1345,7 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>46419</v>
+        <v>46447</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1393,7 +1373,7 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>46447</v>
+        <v>46478</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1421,7 +1401,7 @@
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
-        <v>46478</v>
+        <v>46508</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1449,7 +1429,7 @@
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>46508</v>
+        <v>46539</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1477,7 +1457,7 @@
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
-        <v>46539</v>
+        <v>46569</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1495,37 +1475,9 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>1114.53</v>
+        <v>1114.55</v>
       </c>
       <c r="F43" t="inlineStr">
-        <is>
-          <t>rateio de contrato de 12 meses, total 13374.38</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="n">
-        <v>46569</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>comum</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>consultoria</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Consultoria</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>1114.55</v>
-      </c>
-      <c r="F44" t="inlineStr">
         <is>
           <t>rateio de contrato de 12 meses, total 13374.38</t>
         </is>
